--- a/출장비용2026.xlsx
+++ b/출장비용2026.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Repo\01_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\03_repo\02_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6814AC4-F8AC-4CA7-900B-A6C6E8983800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63976914-0A04-4F75-B69C-602C39D4C4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A1FF4E80-560E-4257-8401-D8F9AF42980E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A1FF4E80-560E-4257-8401-D8F9AF42980E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -246,9 +247,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -286,7 +287,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -392,7 +393,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -534,7 +535,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -549,6 +550,7 @@
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.4">
@@ -646,6 +648,9 @@
       <c r="K8" t="s">
         <v>15</v>
       </c>
+      <c r="O8" s="2">
+        <v>177948</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
       <c r="F9" t="s">
@@ -662,6 +667,15 @@
       </c>
       <c r="K9" t="s">
         <v>15</v>
+      </c>
+      <c r="O9" s="2">
+        <v>252716</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="O10" s="2">
+        <f>SUM(O8:O9)</f>
+        <v>430664</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.4">
@@ -779,4 +793,14 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F304AE-4FD6-48DE-A186-66787C4814AA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>